--- a/companies/dev-mini/Finance/FY2021 Financial Summary.xlsx
+++ b/companies/dev-mini/Finance/FY2021 Financial Summary.xlsx
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>519386</v>
+        <v>431000</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>117280</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>75394</v>
+        <v>84390</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>67017</v>
+        <v>58890</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -539,7 +539,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>58643</v>
+        <v>53720</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>837720</v>
+        <v>720800</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>236280</v>
+        <v>353200</v>
       </c>
     </row>
   </sheetData>

--- a/companies/dev-mini/Finance/FY2021 Financial Summary.xlsx
+++ b/companies/dev-mini/Finance/FY2021 Financial Summary.xlsx
@@ -474,20 +474,20 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>300544</v>
+        <v>273680</v>
       </c>
       <c r="C4" s="3">
-        <v>234093</v>
+        <v>213169</v>
       </c>
       <c r="D4" s="3">
-        <v>244190</v>
+        <v>222363</v>
       </c>
       <c r="E4" s="3">
-        <v>295173</v>
+        <v>268788</v>
       </c>
       <c r="F4" s="4">
         <f>SUM(B4:E4)</f>
-        <v>1074000</v>
+        <v>978000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>431000</v>
+        <v>500900</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>92800</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>84390</v>
+        <v>78810</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>58890</v>
+        <v>60400</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -539,7 +539,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>53720</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>720800</v>
+        <v>790410</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>353200</v>
+        <v>187590</v>
       </c>
     </row>
   </sheetData>
